--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137168904</v>
+        <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>5182</v>
+        <v>96709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövhagen, Upl</t>
+          <t>Låddersta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639481</v>
+        <v>639471</v>
       </c>
       <c r="R4" t="n">
-        <v>6604898</v>
+        <v>6604942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,21 +972,11 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,22 +985,393 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137196726</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137165877</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagalund, Kalmar sn, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>639535</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6604759</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137165877</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137168904</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>639481</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6604898</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137168904</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137165764</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagalund, Kalmar sn, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>639535</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6604755</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137165764</t>
         </is>
       </c>
     </row>
@@ -1019,6 +1380,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -1056,11 +1056,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1288,11 +1284,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>137168904</v>
       </c>
       <c r="B6" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36934-2026 artfynd.xlsx
+++ b/artfynd/A 36934-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137166690</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137166753</v>
       </c>
       <c r="B3" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137196726</v>
       </c>
       <c r="B4" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137165877</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>137165764</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
